--- a/public/data/toefl/14-12-25/toefl.xlsx
+++ b/public/data/toefl/14-12-25/toefl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARVIN3108\Desktop\au-tryout-statistics\public\data\toefl\14-12-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BD60F9-F0CD-4FD7-A79C-2A40EC350B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B5FC32-C74E-4023-8337-C4E9DEE42478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/data/toefl/14-12-25/toefl.xlsx
+++ b/public/data/toefl/14-12-25/toefl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARVIN3108\Desktop\au-tryout-statistics\public\data\toefl\14-12-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B5FC32-C74E-4023-8337-C4E9DEE42478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2B21D-9B55-4BA8-8A01-A5C5E84697E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
